--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97563529</v>
+        <v>95851843</v>
       </c>
       <c r="B2" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älmhult, Srm</t>
+          <t>Slänten 150m v, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606448.7922080299</v>
+        <v>606808</v>
       </c>
       <c r="R2" t="n">
-        <v>6557864.803500718</v>
+        <v>6557731</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,30 +758,342 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>97563529</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Älmhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>606449</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6557865</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Leif Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Emma Karlsson, Lennart Sundh</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97529552</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kvattala, N om vid vägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>606401</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6557861</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1978-05-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1978-05-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>torrbacke på gravfält</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97529312</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvattala, N om vid vägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>606401</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6557861</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1978-05-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1978-05-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>torrbacke på gravfält</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95851843</v>
+        <v>134608148</v>
       </c>
       <c r="B2" t="n">
-        <v>110078</v>
+        <v>99532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>219879</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Getrams</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Polygonatum odoratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Mill.) Druce</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,17 +710,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slänten 150m v, Srm</t>
+          <t>Kvattala N om , Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606808</v>
+        <v>606476</v>
       </c>
       <c r="R2" t="n">
-        <v>6557731</v>
+        <v>6557871</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Frisk gräsmark</t>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>berghällar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97563529</v>
+        <v>95851843</v>
       </c>
       <c r="B3" t="n">
-        <v>102419</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +798,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älmhult, Srm</t>
+          <t>Slänten 150m v, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606449</v>
+        <v>606808</v>
       </c>
       <c r="R3" t="n">
-        <v>6557865</v>
+        <v>6557731</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,37 +870,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Lennart Sundh</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97529552</v>
+        <v>97563529</v>
       </c>
       <c r="B4" t="n">
-        <v>102560</v>
+        <v>102419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,37 +905,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222133</v>
+        <v>221317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvattala, N om vid vägen, Srm</t>
+          <t>Älmhult, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606401</v>
+        <v>606449</v>
       </c>
       <c r="R4" t="n">
-        <v>6557861</v>
+        <v>6557865</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,12 +959,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,28 +983,32 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>torrbacke på gravfält</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Emma Karlsson, Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97529312</v>
+        <v>97529552</v>
       </c>
       <c r="B5" t="n">
-        <v>99754</v>
+        <v>102560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222295</v>
+        <v>222133</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1094,6 +1104,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97529312</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kvattala, N om vid vägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>606401</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6557861</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1978-05-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1978-05-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>torrbacke på gravfält</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97563529</v>
+        <v>134631831</v>
       </c>
       <c r="B4" t="n">
-        <v>102419</v>
+        <v>110159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,37 +905,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älmhult, Srm</t>
+          <t>Kvattala N om , Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606449</v>
+        <v>606476</v>
       </c>
       <c r="R4" t="n">
-        <v>6557865</v>
+        <v>6557871</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,17 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,37 +977,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Vägslänt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Lennart Sundh</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97529552</v>
+        <v>97563529</v>
       </c>
       <c r="B5" t="n">
-        <v>102560</v>
+        <v>102419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,37 +1012,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222133</v>
+        <v>221317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvattala, N om vid vägen, Srm</t>
+          <t>Älmhult, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606401</v>
+        <v>606449</v>
       </c>
       <c r="R5" t="n">
-        <v>6557861</v>
+        <v>6557865</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,12 +1066,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,28 +1090,32 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>torrbacke på gravfält</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Emma Karlsson, Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97529312</v>
+        <v>97529552</v>
       </c>
       <c r="B6" t="n">
-        <v>99754</v>
+        <v>102560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222295</v>
+        <v>222133</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1206,6 +1211,211 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97529312</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kvattala, N om vid vägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>606401</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6557861</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1978-05-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1978-05-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>torrbacke på gravfält</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134631843</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102640</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,48 +1001,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97563529</v>
+        <v>134633126</v>
       </c>
       <c r="B5" t="n">
-        <v>102419</v>
+        <v>106358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221317</v>
+        <v>221157</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Älmhult, Srm</t>
+          <t>Kvattala N om , Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606449</v>
+        <v>606476</v>
       </c>
       <c r="R5" t="n">
-        <v>6557865</v>
+        <v>6557871</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,17 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,37 +1084,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Lennart Sundh</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97529552</v>
+        <v>97563529</v>
       </c>
       <c r="B6" t="n">
-        <v>102560</v>
+        <v>102419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,37 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222133</v>
+        <v>221317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvattala, N om vid vägen, Srm</t>
+          <t>Älmhult, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606401</v>
+        <v>606449</v>
       </c>
       <c r="R6" t="n">
-        <v>6557861</v>
+        <v>6557865</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,12 +1173,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,28 +1197,32 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>torrbacke på gravfält</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Emma Karlsson, Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97529312</v>
+        <v>134633252</v>
       </c>
       <c r="B7" t="n">
-        <v>99754</v>
+        <v>102496</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,37 +1230,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222295</v>
+        <v>221317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvattala, N om vid vägen, Srm</t>
+          <t>Kvattala N om , Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606401</v>
+        <v>606476</v>
       </c>
       <c r="R7" t="n">
-        <v>6557861</v>
+        <v>6557871</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,12 +1288,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1978-05-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,33 +1302,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>torrbacke på gravfält</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134631843</v>
+        <v>97529552</v>
       </c>
       <c r="B8" t="n">
-        <v>102640</v>
+        <v>102560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,37 +1337,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>265350</v>
+        <v>222133</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanligt jungfrulin</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygala vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvattala N om , Srm</t>
+          <t>Kvattala, N om vid vägen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606476</v>
+        <v>606401</v>
       </c>
       <c r="R8" t="n">
-        <v>6557871</v>
+        <v>6557861</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>1978-05-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>1978-05-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,27 +1405,963 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Vägslänt</t>
+          <t>torrbacke på gravfält</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97529312</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kvattala, N om vid vägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>606401</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6557861</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1978-05-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1978-05-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>torrbacke på gravfält</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134633109</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Torr gräsmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134633097</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134633093</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134651362</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102871</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gräsmark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134633106</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107697</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>224273</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig ängskovall</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. pratense</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Torr gräsmark</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134651249</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101823</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>224932</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vanlig backsmörblomma</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134633276</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103908</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>225103</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vanlig sälg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134631843</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102640</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kvattala N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>606476</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6557871</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9066-2025 artfynd.xlsx
+++ b/artfynd/A 9066-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134608148</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95851843</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134631831</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134633126</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97563529</t>
         </is>
       </c>
     </row>
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134633252</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97529552</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97529312</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134633109</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134633097</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134633093</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651362</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2058,6 +2123,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134633106</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651249</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2259,6 +2334,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134633276</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2362,8 +2442,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134631843</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>